--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_793_Turkey_Mediterranean_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_793_Turkey_Mediterranean_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R9c49e70d593a4f25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R7da7f24f65a24c29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re34c5405247a45d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rf01102953e494fb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9317037d40c74aff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R293e69bac4944ff0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R937f2ba2249a4c98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rd9053d2748764f3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re3c4f387d4fa4e8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rec047737609e48d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R1ffdc597d7b64947"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R07e32d9d95b64dfa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ793CommercialTable" displayName="EEZ793CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ793CommercialTable" displayName="EEZ793CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ793FunctionalTable" displayName="EEZ793FunctionalTable" ref="A1:O23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O23"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ793FunctionalTable" displayName="EEZ793FunctionalTable" ref="A1:E23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E23"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ793ValidationTable" displayName="EEZ793ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ793ValidationTable" displayName="EEZ793ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6858,7 +6812,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c4ec2ea62544d1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b2a054b45c640dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6868,20 +6822,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6889,660 +6833,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>17552.3964534792</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>17552.3964534792</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$93,A2,'Species'!$U$2:$U$93))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2261186.686233473</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>2261186.686233473</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1750.3818296807</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.347602750330159</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2226.397728993924</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1750.3818296807</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2232.547728693104</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$93,A3,'Species'!$U$2:$U$93))</x:f>
-        <x:v>3907810.978199327</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.347602750330159</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2226.397728993924</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3897046.13047334</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>10764.847725986969</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.002762309545635</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.002762309545635134</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>4262.113808886</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.0546813181363754</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>113.41782591916564</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>4262.113808886</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>198.41901380220472</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$93,A4,'Species'!$U$2:$U$93))</x:f>
-        <x:v>845684.4186719185</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.0546813181363754</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>113.41782591916564</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>483399.68202390434</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>362284.7366480141</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.7494517479432246</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.7494517479432247</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>423.32524207880004</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.2100145277204937</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>162.18643499429507</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>423.32524207880004</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>162.2079010094316</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$93,A5,'Species'!$U$2:$U$93))</x:f>
-        <x:v>68666.69896191166</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.2100145277204937</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>162.18643499429507</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>68657.61185585753</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>9.08710605413944</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0001323539489433</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0001323539489433053</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>22854.9670240415</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.1454693719003086</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>139.78783281467364</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>22854.9670240415</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>200.93543051205637</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$93,A6,'Species'!$U$2:$U$93))</x:f>
-        <x:v>4592372.638314631</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.1454693719003086</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>139.78783281467364</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3194846.3093415922</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1397526.3289730386</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.437431473585046</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.4374314735850461</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>5417.2912701571995</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.709814746611869</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>51.2642663624887</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>5417.2912701571995</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>53.756064238402644</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$93,A7,'Species'!$U$2:$U$93))</x:f>
-        <x:v>291212.2575167083</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.709814746611869</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>51.2642663624887</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>277713.4626365234</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>13498.794880184869</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0486069157470135</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.04860691574701348</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>9071.6424499165</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.4412871357509895</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>276.24036281844616</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>9071.6424499165</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>535.1700134872951</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$93,A8,'Species'!$U$2:$U$93))</x:f>
-        <x:v>4854871.012273733</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.4412871357509895</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>276.24036281844616</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>2505953.8017241517</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2348917.210549581</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.937334602470913</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.937334602470913</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>21592.642587422702</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.2163098266836134</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>164.55452403345626</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>21592.642587422702</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>484.09215026471753</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$93,A9,'Species'!$U$2:$U$93))</x:f>
-        <x:v>10452828.78004297</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.2163098266836134</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>164.55452403345626</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>3553167.0235978803</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>6899661.75644509</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.9418343440153296</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.9418343440153294</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>334.2515210217</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.890746208481109</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>777.5820175325306</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>334.2515210217</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>795.4614502176466</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$93,A10,'Species'!$U$2:$U$93))</x:f>
-        <x:v>265884.1996493757</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.890746208481109</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>777.5820175325306</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>259907.97207937055</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>5976.22757000514</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0229936293303852</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.02299362933038515</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>294.79965577699994</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.014133661725195</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1033.0793050701773</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>294.79965577699994</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1070.7154155183384</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$93,A11,'Species'!$U$2:$U$93))</x:f>
-        <x:v>315646.53592993366</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.014133661725195</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1033.0793050701773</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>304551.42352503055</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>11095.112404903106</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0364309983400595</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.03643099834005937</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>3501.6045853580003</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.430748383825912</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2696.1769021687405</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>3501.6045853580003</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2806.23334348652</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$93,A12,'Species'!$U$2:$U$93))</x:f>
-        <x:v>9826319.543136911</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.430748383825912</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2696.1769021687405</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>9440945.403570391</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>385374.1395665202</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0408194437201999</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.040819443720199765</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc79203fd7f4b4f72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a152f3e23e248cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7552,20 +7067,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7573,1254 +7078,440 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1638.3214245985998</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.099289957493284</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1256.868834368645</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1638.3214245985998</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1487.5627219998644</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$93,A2,'Species'!$U$2:$U$93))</x:f>
-        <x:v>2437105.8778865887</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.099289957493284</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1256.868834368645</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>2059155.1392564198</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>377950.73863016884</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1835465096460145</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.18354650964601452</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1424.7407963381002</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.367135804418999</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2328.819368501223</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1424.7407963381002</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2338.0508496564134</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$93,A3,'Species'!$U$2:$U$93))</x:f>
-        <x:v>3331116.42941845</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.367135804418999</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2328.819368501223</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3317963.961606024</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>13152.467812426388</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.003964017682115</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0039640176821149325</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>870.8147337356</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.496121301677226</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>3134.160996539734</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>870.8147337356</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>3210.1923088968874</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$93,A4,'Species'!$U$2:$U$93))</x:f>
-        <x:v>2795482.760712114</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.496121301677226</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>3134.160996539734</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>2729273.573686251</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>66209.18702586321</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.02425890451738</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.024258904517379987</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>1204.0647481496003</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.8666024657329774</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>735.5335138910723</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>1204.0647481496003</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>766.2538654976513</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$93,A5,'Species'!$U$2:$U$93))</x:f>
-        <x:v>922619.2675790872</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.8666024657329774</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>735.5335138910723</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>885629.9751588445</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>36989.29242024268</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0417660800308937</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.04176608003089368</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>0.0053477833</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.36</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2290.867652767775</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>0.0053477833</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$93,A6,'Species'!$U$2:$U$93))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>12.251063775981704</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.36</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2290.867652767775</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>12.251063775981704</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2204.6228006058</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.469540363545849</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2948.087460593819</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2204.6228006058</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2966.0402047006046</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$93,A7,'Species'!$U$2:$U$93))</x:f>
-        <x:v>6538999.862796447</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.469540363545849</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2948.087460593819</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>6499420.833805186</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>39579.0289912615</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0060896239839403</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.006089623983940327</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>67.9537846506</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.84</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>691.8309709189363</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>67.9537846506</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$93,A8,'Species'!$U$2:$U$93))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>47012.532812440906</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.84</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>691.8309709189363</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>47012.532812440906</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>23.055057591200004</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.486966509585918</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>3068.785331333382</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>23.055057591200004</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>3074.628767249516</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$93,A9,'Species'!$U$2:$U$93))</x:f>
-        <x:v>70885.74330049787</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.486966509585918</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>3068.785331333382</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>70751.02254892091</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>134.72075157695508</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0019041527136063</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0019041527136063963</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>226.84587112640003</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.066297015153394</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1164.922450610181</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>226.84587112640003</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1184.2137649832212</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$93,A10,'Species'!$U$2:$U$93))</x:f>
-        <x:v>268634.0031174928</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.066297015153394</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1164.922450610181</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>264257.8481033672</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>4376.155014125572</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0165601704756704</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.01656017047567039</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1257.2007717540002</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.4141257161398837</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>259.4930413390518</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1257.2007717540002</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>304.4605986849638</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$93,A11,'Species'!$U$2:$U$93))</x:f>
-        <x:v>382768.0996354215</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.4141257161398837</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>259.4930413390518</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>326234.8518362486</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>56533.24779917288</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1732900316473525</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.17329003164735252</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>21.0100592947</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.5159971272912007</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>328.0931228826474</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>21.0100592947</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>328.8664141423999</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$93,A12,'Species'!$U$2:$U$93))</x:f>
-        <x:v>6909.502861167188</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.5159971272912007</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>328.0931228826474</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>6893.255965947715</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>16.246895219473117</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0023569261463279</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.002356926146327924</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>3303.7961704501</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.236678434889494</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>172.45605010307466</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>3303.7961704501</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>550.7977922139265</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$93,A13,'Species'!$U$2:$U$93))</x:f>
-        <x:v>1819723.6366087403</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.236678434889494</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>172.45605010307466</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>569759.6379014886</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1249963.9987072516</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>3.193844413604058</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>2.193844413604058</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>15119.6863698537</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.994456044405337</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>98.73157029894439</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>15119.6863698537</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>131.383726254504</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$93,A14,'Species'!$U$2:$U$93))</x:f>
-        <x:v>1986480.735070814</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.994456044405337</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>98.73157029894439</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1492790.3777232019</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>493690.35734761204</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.3307164654293837</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.33071646542938377</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>7680.6244116935</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>4.022150616261291</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>1052.3267645798671</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>7680.6244116935</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1351.9298936964037</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$93,A15,'Species'!$U$2:$U$93))</x:f>
-        <x:v>10383665.744422797</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>4.022150616261291</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>1052.3267645798671</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>8082526.637110567</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>2301139.1073122304</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2847054158469025</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.2847054158469025</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>1935.3520073249</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.9926249371979257</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>98.31616668238028</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>1935.3520073249</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>266.23745670367174</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$93,A16,'Species'!$U$2:$U$93))</x:f>
-        <x:v>515263.19625652727</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.9926249371979257</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>98.31616668238028</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>190276.39054123414</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>324986.80571529316</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>2.707972306973452</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>1.7079723069734518</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>5884.5039785328</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.6875982597023707</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>48.70777146789039</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>5884.5039785328</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>51.624988491681044</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$93,A17,'Species'!$U$2:$U$93))</x:f>
-        <x:v>303787.45017100713</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.6875982597023707</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>48.70777146789039</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>286621.0749882674</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>17166.37518273975</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0598922294302415</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.05989222943024145</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>3004.913037132</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.904296342268997</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>80.22252777280886</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>3004.913037132</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>154.05315006331145</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$93,A18,'Species'!$U$2:$U$93))</x:f>
-        <x:v>462916.31903649704</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.904296342268997</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>80.22252777280886</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>241061.7195761973</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>221854.59946029974</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.9203228113129494</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.9203228113129494</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>413.2545821036</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.58539817587901</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>384.94455049734256</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>413.2545821036</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>395.2216192247399</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$93,A19,'Species'!$U$2:$U$93))</x:f>
-        <x:v>163327.145091028</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.58539817587901</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>384.94455049734256</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>159080.09934883745</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>4247.045742190559</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.0266975301095171</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.0266975301095171</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>1119.5874440539</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.3907421144974386</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>245.89070633907656</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>1119.5874440539</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>368.38056302055764</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$93,A20,'Species'!$U$2:$U$93))</x:f>
-        <x:v>412434.2529913228</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.3907421144974386</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>245.89070633907656</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>275296.14742677484</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>137138.10556454794</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.4981475652543408</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.4981475652543408</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>38872.4748980388</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.083057133763731</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>121.07574046911432</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>38872.4748980388</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>121.38156337693549</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$93,A21,'Species'!$U$2:$U$93))</x:f>
-        <x:v>4718401.775454631</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.083057133763731</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>121.07574046911432</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>4706513.682147107</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>11888.093307523988</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.002525880962084</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.002525880962084158</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>359.2682387126</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.1100000000000003</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>128.82495516931348</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>359.2682387126</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$93,A22,'Species'!$U$2:$U$93))</x:f>
-        <x:v>46282.714745908874</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.1100000000000003</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>128.82495516931348</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>46282.71474590891</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>-3.637978807091713e-11</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>0.9999999999999992</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>-7.860340144401937e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>423.31989429550003</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.21</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>162.18100973589299</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>423.31989429550003</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>162.18100973589299</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$93,A23,'Species'!$U$2:$U$93))</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>68654.44789813568</x:v>
       </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.21</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>162.18100973589299</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
-        <x:v>68654.44789813568</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G23">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O23">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdae0405273284ffb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R791d6a03e47f4192"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8995,7 +7686,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -9094,7 +7785,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>37682483.748930894</x:v>
+        <x:v>26247375.507061515</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9108,7 +7799,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>37682483.748930894</x:v>
+        <x:v>32325468.175251145</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9122,7 +7813,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-1.4901161193847656e-8</x:v>
+        <x:v>-11435108.241869394</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9136,7 +7827,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-1.4901161193847656e-8</x:v>
+        <x:v>-5357015.573679764</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -9147,9 +7838,9 @@
         <x:v>EEZ_793</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -9161,47 +7852,19 @@
         <x:v>EEZ_793</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_793</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_793</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2df8ae0cb3d4867"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3c56fe6a9974dd8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9248,7 +7911,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
